--- a/docs/Data_Dictionary_volume.xlsx
+++ b/docs/Data_Dictionary_volume.xlsx
@@ -644,7 +644,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sinh tự động từ catalog PostgreSQL reportapi — bronze.ins_* (v2/docs/build_docs.py, DOCS_TARGET=volume) ngày 16/10/2026. Tên bảng ghi theo mô hình logic: ref.X / core.X = bronze.ins_X.</t>
+          <t>Sinh tự động từ catalog PostgreSQL reportapi — bronze.ins_* (scripts/build_docs.py, DOCS_TARGET=volume) ngày 19/10/2026. Tên bảng ghi theo mô hình logic: ref.X / core.X = bronze.ins_X.</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Toàn bộ dữ liệu là giả lập: doanh nghiệp 'DEMO', đối tác và DN đồng bảo hiểm ẩn danh, khách hàng sinh ngẫu nhiên.</t>
+          <t>Danh mục doanh nghiệp là Tổng Công ty Bảo hiểm PVI với 47 đơn vị thật (pvi.com.vn/vi/network); 3 đối tác số có công bố hợp tác với PVI mang tên thật (Green SM, ATADI, Fuse); các đối tác khác và DN đồng bảo hiểm ẩn danh. Mọi giao dịch, số tiền, khách hàng là giả lập — không phải số liệu thật của PVI hay của từng đơn vị.</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -2350,11 +2350,11 @@
       <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>CHN_BB | CHN_TN | NG_DL_ND</t>
+          <t>CHN_BB | CHN_TN | MV_DELAYCARE</t>
         </is>
       </c>
       <c r="K15" s="9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L15" s="20" t="n">
         <v>0</v>
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="K16" s="9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L16" s="20" t="n">
         <v>0</v>
@@ -2701,7 +2701,7 @@
         <v>3</v>
       </c>
       <c r="L23" s="20" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.3043478260869565</v>
       </c>
     </row>
     <row r="24">
@@ -2738,11 +2738,11 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>1 Medical expense insurance | 1 Medical expense insurance (*) | 2 Income protection insurance (*)</t>
+          <t>12 Miscellaneous financial loss (*) | 1 Medical expense insurance | 1 Medical expense insurance (*)</t>
         </is>
       </c>
       <c r="K24" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L24" s="20" t="n">
         <v>0</v>
@@ -3030,12 +3030,12 @@
     <row r="40">
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>NG_DL_ND</t>
+          <t>MV_DELAYCARE</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm du lịch trong nước</t>
+          <t>Bảo hiểm trễ chuyến bay (DelayCare)</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -3071,29 +3071,29 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>1 Medical expense insurance (*)</t>
+          <t>12 Miscellaneous financial loss (*)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>NG_DL_QT</t>
+          <t>MV_FOOD_CARE</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm du lịch quốc tế</t>
+          <t>Bảo hiểm đơn giao đồ ăn (Food Care)</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>DU_LICH</t>
+          <t>SINH_MANG</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>A.2</t>
+          <t>A.1</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -3119,29 +3119,29 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>1 Medical expense insurance (*)</t>
+          <t>2 Income protection insurance (*)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>NG_HSSV_SK</t>
+          <t>MV_TBDT_TMDT</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm sức khỏe toàn diện học sinh, sinh viên</t>
+          <t>Bảo hiểm thiết bị điện tử mua trên sàn TMĐT</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>HOC_SINH</t>
+          <t>TAI_SAN</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>A.2</t>
+          <t>B.1b</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -3151,23 +3151,19 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>PER_PERSON</t>
+          <t>RATE_ON_SI</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>Không chịu thuế GTGT – Luật Thuế GTGT 48/2024/QH15 Điều 5 k8</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J42" s="5" t="inlineStr"/>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>1 Medical expense insurance</t>
+          <t>7 Fire and other damage to property insurance (*)</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3601,7 @@
       <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>01 | 2 | 3</t>
+          <t>1 | 2 | 3</t>
         </is>
       </c>
       <c r="K19" s="9" t="n">
@@ -3893,7 +3889,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -3946,7 +3942,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ref.partner — Đối tác phân phối (ẩn danh) — ngân hàng, đăng kiểm, OTA, ví điện tử...</t>
+          <t>ref.partner — Đối tác phân phối — ngân hàng, đăng kiểm, OTA, ví điện tử... (ẩn danh); 3 đối tác số tên thật có công bố hợp tác với PVI: Green SM, ATADI, Fuse</t>
         </is>
       </c>
     </row>
@@ -4002,7 +3998,7 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Đối tác phân phối (ẩn danh) — ngân hàng, đăng kiểm, OTA, ví điện tử...</t>
+          <t>Đối tác phân phối — ngân hàng, đăng kiểm, OTA, ví điện tử... (ẩn danh); 3 đối tác số tên thật có công bố hợp tác với PVI: Green SM, ATADI, Fuse</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4044,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
@@ -4059,7 +4055,7 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>Loại đối tác theo thực tế thị trường; tên ẩn danh</t>
+          <t>Loại đối tác theo thực tế thị trường; đối tác truyền thống ẩn danh, đối tác bảo hiểm vi mô theo nguồn công khai (sources/market_data.md mục 10)</t>
         </is>
       </c>
     </row>
@@ -4160,11 +4156,11 @@
       <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>BC_A | CTTC_A | CTTC_B</t>
+          <t>ATADI | BC_A | CTTC_A</t>
         </is>
       </c>
       <c r="K15" s="9" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L15" s="20" t="n">
         <v>0</v>
@@ -4194,17 +4190,17 @@
       <c r="G16" s="6" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Tên đối tác (ẩn danh: Ngân hàng TMCP A, Ví điện tử B …)</t>
+          <t>Tên đối tác (ẩn danh: Ngân hàng TMCP A, Ví điện tử B …; tên thật cho Green SM, ATADI, Fuse)</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Công ty lữ hành A | Công ty lữ hành B | Công ty lữ hành C</t>
+          <t>ATADI.vn – đại lý vé máy bay trực tuyến | Công ty lữ hành A | Công ty lữ hành B</t>
         </is>
       </c>
       <c r="K16" s="9" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L16" s="20" t="n">
         <v>0</v>
@@ -4244,7 +4240,7 @@
         </is>
       </c>
       <c r="K17" s="9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L17" s="20" t="n">
         <v>0</v>
@@ -4432,56 +4428,56 @@
     <row r="31">
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>BC_A</t>
+          <t>ATADI</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Mạng lưới bưu cục A</t>
+          <t>ATADI.vn – đại lý vé máy bay trực tuyến</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>BUU_CHINH</t>
+          <t>OTA_VE_MAY_BAY</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>DAI_LY_TC</t>
+          <t>DIEN_TU</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>CTTC_A</t>
+          <t>BC_A</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Công ty tài chính A</t>
+          <t>Mạng lưới bưu cục A</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>CTY_TAI_CHINH</t>
+          <t>BUU_CHINH</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>BANCA</t>
+          <t>DAI_LY_TC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>CTTC_B</t>
+          <t>CTTC_A</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Công ty tài chính B</t>
+          <t>Công ty tài chính A</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -4498,34 +4494,34 @@
     <row r="34">
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>DK_A</t>
+          <t>CTTC_B</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Trung tâm đăng kiểm A</t>
+          <t>Công ty tài chính B</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>DANG_KIEM</t>
+          <t>CTY_TAI_CHINH</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>DAI_LY_TC</t>
+          <t>BANCA</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>DK_B</t>
+          <t>DK_A</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Trung tâm đăng kiểm B</t>
+          <t>Trung tâm đăng kiểm A</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -5243,7 +5239,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>1917522</v>
+        <v>1696375</v>
       </c>
     </row>
     <row r="12">
@@ -5355,11 +5351,11 @@
       <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>KH310000001 | KH310000002 | KH310000003</t>
+          <t>KH610000001 | KH610000002 | KH610000003</t>
         </is>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1917522</v>
+        <v>1696375</v>
       </c>
       <c r="L15" s="20" t="n">
         <v>0</v>
@@ -5399,11 +5395,11 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Ban Quản lý dự án An Giang | Ban Quản lý dự án Bắc Ninh | Ban Quản lý dự án Cà Mau</t>
+          <t>Ban Quản lý dự án Bắc Ninh | Ban Quản lý dự án Cà Mau | Ban Quản lý dự án Cần Thơ</t>
         </is>
       </c>
       <c r="K16" s="9" t="n">
-        <v>61788</v>
+        <v>48530</v>
       </c>
       <c r="L16" s="20" t="n">
         <v>0</v>
@@ -5479,14 +5475,14 @@
       <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>0100007882 | 0100050897 | 0100056368</t>
+          <t>0100037302 | 0100065094 | 0100068691</t>
         </is>
       </c>
       <c r="K18" s="9" t="n">
-        <v>39627</v>
+        <v>15879</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>0.9793342657867811</v>
+        <v>0.9906394517721612</v>
       </c>
     </row>
     <row r="19">
@@ -5563,11 +5559,11 @@
       <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>AGG | BNH | CTO</t>
+          <t>AGI | ALC | BTB</t>
         </is>
       </c>
       <c r="K20" s="9" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="L20" s="20" t="n">
         <v>0</v>
@@ -5690,7 +5686,7 @@
         <v>2</v>
       </c>
       <c r="L23" s="20" t="n">
-        <v>0.02067512132846455</v>
+        <v>0.009387664873627589</v>
       </c>
     </row>
     <row r="24">
@@ -5730,7 +5726,7 @@
         <v>63</v>
       </c>
       <c r="L24" s="20" t="n">
-        <v>0.02067512132846455</v>
+        <v>0.009387664873627589</v>
       </c>
     </row>
     <row r="25"/>
@@ -5945,12 +5941,12 @@
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>KH310000001</t>
+          <t>KH610000001</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Lê Xuân Vinh</t>
+          <t>Hoàng Gia Nam</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -5966,7 +5962,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DHI</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -5975,7 +5971,7 @@
         </is>
       </c>
       <c r="I39" s="24" t="n">
-        <v>45400</v>
+        <v>46107</v>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
@@ -5983,18 +5979,18 @@
         </is>
       </c>
       <c r="K39" s="5" t="n">
-        <v>1981</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>KH310000002</t>
+          <t>KH610000002</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Nguyễn Xuân Khánh</t>
+          <t>Đoàn Văn Phong</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -6010,7 +6006,7 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>HN1</t>
+          <t>HNO</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -6019,7 +6015,7 @@
         </is>
       </c>
       <c r="I40" s="24" t="n">
-        <v>45898</v>
+        <v>43560</v>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
@@ -6027,18 +6023,18 @@
         </is>
       </c>
       <c r="K40" s="5" t="n">
-        <v>1978</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>KH310000003</t>
+          <t>KH610000003</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Phạm Công Bình</t>
+          <t>Hoàng Thanh Quyên</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -6054,7 +6050,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>BTB</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -6063,26 +6059,26 @@
         </is>
       </c>
       <c r="I41" s="24" t="n">
-        <v>46235</v>
+        <v>44289</v>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="K41" s="5" t="n">
-        <v>1974</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>KH310000004</t>
+          <t>KH610000004</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Huỳnh Hoàng Lộc</t>
+          <t>Vũ Tuấn Khoa</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -6098,7 +6094,7 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>HC1</t>
+          <t>TDH</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
@@ -6115,18 +6111,18 @@
         </is>
       </c>
       <c r="K42" s="5" t="n">
-        <v>1985</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>KH310000005</t>
+          <t>KH610000005</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Nguyễn Hải Hoa</t>
+          <t>Nguyễn Công Tài</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -6142,7 +6138,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CLG</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -6151,15 +6147,15 @@
         </is>
       </c>
       <c r="I43" s="24" t="n">
-        <v>45267</v>
+        <v>46235</v>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>1989</v>
+        <v>1968</v>
       </c>
     </row>
   </sheetData>
@@ -8127,7 +8123,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sinh tự động từ catalog PostgreSQL reportapi — bronze.ins_* (v2/docs/build_docs.py, DOCS_TARGET=volume) ngày 16/10/2026. Tên bảng ghi theo mô hình logic: ref.X / core.X = bronze.ins_X.</t>
+          <t>Sinh tự động từ catalog PostgreSQL reportapi — bronze.ins_* (scripts/build_docs.py, DOCS_TARGET=volume) ngày 19/10/2026. Tên bảng ghi theo mô hình logic: ref.X / core.X = bronze.ins_X.</t>
         </is>
       </c>
     </row>
@@ -8317,7 +8313,7 @@
         <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
@@ -8505,7 +8501,7 @@
         <v/>
       </c>
       <c r="I11" s="9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
@@ -8581,7 +8577,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Đối tác phân phối (ẩn danh) — ngân hàng, đăng kiểm, OTA, ví điện tử...</t>
+          <t>Đối tác phân phối — ngân hàng, đăng kiểm, OTA, ví điện tử... (ẩn danh); 3 đối tác số tên thật có công bố hợp tác với PVI: Green SM, ATADI, Fuse</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -8599,11 +8595,11 @@
         <v/>
       </c>
       <c r="I13" s="9" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Loại đối tác theo thực tế thị trường; tên ẩn danh</t>
+          <t>Loại đối tác theo thực tế thị trường; đối tác truyền thống ẩn danh, đối tác bảo hiểm vi mô theo nguồn công khai (sources/market_data.md mục 10)</t>
         </is>
       </c>
     </row>
@@ -8693,7 +8689,7 @@
         <v/>
       </c>
       <c r="I15" s="9" t="n">
-        <v>1917522</v>
+        <v>1696375</v>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
@@ -8975,7 +8971,7 @@
         <v/>
       </c>
       <c r="I21" s="9" t="n">
-        <v>4669144</v>
+        <v>4082637</v>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
@@ -9022,7 +9018,7 @@
         <v/>
       </c>
       <c r="I22" s="9" t="n">
-        <v>4717930</v>
+        <v>4098401</v>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
@@ -9069,7 +9065,7 @@
         <v/>
       </c>
       <c r="I23" s="9" t="n">
-        <v>4844773</v>
+        <v>4127680</v>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
@@ -9116,7 +9112,7 @@
         <v/>
       </c>
       <c r="I24" s="9" t="n">
-        <v>4670512</v>
+        <v>4082967</v>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
@@ -9163,7 +9159,7 @@
         <v/>
       </c>
       <c r="I25" s="9" t="n">
-        <v>4991277</v>
+        <v>4152252</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
@@ -10427,7 +10423,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>4669144</v>
+        <v>4082637</v>
       </c>
     </row>
     <row r="12">
@@ -10539,11 +10535,11 @@
       <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>30000001 | 30000002 | 30000003</t>
+          <t>60000001 | 60000002 | 60000003</t>
         </is>
       </c>
       <c r="K15" s="9" t="n">
-        <v>4669144</v>
+        <v>4082637</v>
       </c>
       <c r="L15" s="20" t="n">
         <v>0</v>
@@ -10583,11 +10579,11 @@
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>2026-AGG-BHN-3000001 | 2026-AGG-BHN-3000002 | 2026-AGG-BHN-3000003</t>
+          <t>2026-AGI-BHN-2000001 | 2026-AGI-BHN-2000002 | 2026-AGI-BHN-2000003</t>
         </is>
       </c>
       <c r="K16" s="9" t="n">
-        <v>4669144</v>
+        <v>4082637</v>
       </c>
       <c r="L16" s="20" t="n">
         <v>0</v>
@@ -10627,11 +10623,11 @@
       <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>AGG | BNH | CTO</t>
+          <t>AGI | ALC | BTB</t>
         </is>
       </c>
       <c r="K17" s="9" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="L17" s="20" t="n">
         <v>0</v>
@@ -10671,11 +10667,11 @@
       <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>KH310000001 | KH310000002 | KH310000003</t>
+          <t>KH610000001 | KH610000002 | KH610000003</t>
         </is>
       </c>
       <c r="K18" s="9" t="n">
-        <v>1917522</v>
+        <v>1696375</v>
       </c>
       <c r="L18" s="20" t="n">
         <v>0</v>
@@ -10722,7 +10718,7 @@
         <v>7</v>
       </c>
       <c r="L19" s="20" t="n">
-        <v>0.005034970007350384</v>
+        <v>0.001144603353175901</v>
       </c>
     </row>
     <row r="20">
@@ -10759,14 +10755,14 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>BC_A | CTTC_A | CTTC_B</t>
+          <t>ATADI | BC_A | CTTC_A</t>
         </is>
       </c>
       <c r="K20" s="9" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L20" s="20" t="n">
-        <v>0.5678167132990544</v>
+        <v>0.1219361407835181</v>
       </c>
     </row>
     <row r="21">
@@ -10887,7 +10883,7 @@
         </is>
       </c>
       <c r="K23" s="9" t="n">
-        <v>797</v>
+        <v>778</v>
       </c>
       <c r="L23" s="20" t="n">
         <v>0</v>
@@ -10927,7 +10923,7 @@
         </is>
       </c>
       <c r="K24" s="9" t="n">
-        <v>996</v>
+        <v>979</v>
       </c>
       <c r="L24" s="20" t="n">
         <v>0</v>
@@ -10999,14 +10995,14 @@
       <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>2025-AGG-BHN-0035618 | 2025-AGG-BHN-0041851 | 2025-AGG-BHN-0051363</t>
+          <t>2025-AGI-BHN-0264157 | 2025-AGI-BHN-0486076 | 2025-AGI-BHN-0661096</t>
         </is>
       </c>
       <c r="K26" s="9" t="n">
-        <v>720041</v>
+        <v>172888</v>
       </c>
       <c r="L26" s="20" t="n">
-        <v>0.8455573441298876</v>
+        <v>0.9576472265352026</v>
       </c>
     </row>
     <row r="27">
@@ -11403,29 +11399,33 @@
     </row>
     <row r="48">
       <c r="B48" s="5" t="n">
-        <v>30000001</v>
+        <v>60000001</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>2026-HN2-T24-3000001</t>
+          <t>2026-DGT-XSC-6000001</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>HN2</t>
+          <t>DGT</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>KH310312794</t>
+          <t>KH670050988</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>DAI_LY_CN</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr"/>
+          <t>DIEN_TU</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>GREEN_SM</t>
+        </is>
+      </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
           <t>VND</t>
@@ -11438,7 +11438,7 @@
         <v>46235</v>
       </c>
       <c r="K48" s="24" t="n">
-        <v>46599</v>
+        <v>46235</v>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
@@ -11450,21 +11450,21 @@
     </row>
     <row r="49">
       <c r="B49" s="5" t="n">
-        <v>30000002</v>
+        <v>60000002</v>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>2026-HPG-DLN-3000001</t>
+          <t>2026-DGT-FDC-2000001</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DGT</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>KH310000001</t>
+          <t>KH670074759</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -11472,7 +11472,11 @@
           <t>DIEN_TU</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr"/>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>GREEN_SM</t>
+        </is>
+      </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
           <t>VND</t>
@@ -11482,14 +11486,14 @@
         <v>46235</v>
       </c>
       <c r="J49" s="24" t="n">
-        <v>46510</v>
+        <v>46235</v>
       </c>
       <c r="K49" s="24" t="n">
-        <v>46512</v>
+        <v>46235</v>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr"/>
@@ -11497,29 +11501,33 @@
     </row>
     <row r="50">
       <c r="B50" s="5" t="n">
-        <v>30000003</v>
+        <v>60000003</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>2026-AGG-TXM-3000001</t>
+          <t>2026-DGT-TBD-2000001</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>DGT</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>KH310961611</t>
+          <t>KH670605908</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>DAI_LY_CN</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr"/>
+          <t>DIEN_TU</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>FUSE</t>
+        </is>
+      </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
           <t>VND</t>
@@ -11544,31 +11552,31 @@
     </row>
     <row r="51">
       <c r="B51" s="5" t="n">
-        <v>30000004</v>
+        <v>60000004</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>2026-HN3-TSN-3000001</t>
+          <t>2026-DGT-FDC-2000002</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>HN3</t>
+          <t>DGT</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>KH320061676</t>
+          <t>KH670129618</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>BANCA</t>
+          <t>DIEN_TU</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>NH_A</t>
+          <t>GREEN_SM</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -11583,7 +11591,7 @@
         <v>46235</v>
       </c>
       <c r="K51" s="24" t="n">
-        <v>46599</v>
+        <v>46235</v>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
@@ -11595,21 +11603,21 @@
     </row>
     <row r="52">
       <c r="B52" s="5" t="n">
-        <v>30000005</v>
+        <v>60000005</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>2026-HPG-T24-3000001</t>
+          <t>2026-DGT-FDC-2000003</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DGT</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>KH310000001</t>
+          <t>KH670349391</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -11617,7 +11625,11 @@
           <t>DIEN_TU</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr"/>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>GREEN_SM</t>
+        </is>
+      </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
           <t>VND</t>
@@ -11630,7 +11642,7 @@
         <v>46235</v>
       </c>
       <c r="K52" s="24" t="n">
-        <v>46599</v>
+        <v>46235</v>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
@@ -11805,7 +11817,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>4717930</v>
+        <v>4098401</v>
       </c>
     </row>
     <row r="12">
@@ -11917,11 +11929,11 @@
       <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>30000001 | 30000002 | 30000003</t>
+          <t>60000001 | 60000002 | 60000003</t>
         </is>
       </c>
       <c r="K15" s="9" t="n">
-        <v>4717930</v>
+        <v>4098401</v>
       </c>
       <c r="L15" s="20" t="n">
         <v>0</v>
@@ -11961,11 +11973,11 @@
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>30000001 | 30000002 | 30000003</t>
+          <t>60000001 | 60000002 | 60000003</t>
         </is>
       </c>
       <c r="K16" s="9" t="n">
-        <v>4669144</v>
+        <v>4082637</v>
       </c>
       <c r="L16" s="20" t="n">
         <v>0</v>
@@ -12001,11 +12013,11 @@
       <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>2026-AGG-BHN-3000001/00 | 2026-AGG-BHN-3000002/00 | 2026-AGG-BHN-3000003/00</t>
+          <t>2026-AGI-BHN-2000001/00 | 2026-AGI-BHN-2000002/00 | 2026-AGI-BHN-2000003/00</t>
         </is>
       </c>
       <c r="K17" s="9" t="n">
-        <v>4717930</v>
+        <v>4098401</v>
       </c>
       <c r="L17" s="20" t="n">
         <v>0</v>
@@ -12133,7 +12145,7 @@
         </is>
       </c>
       <c r="K20" s="9" t="n">
-        <v>797</v>
+        <v>778</v>
       </c>
       <c r="L20" s="20" t="n">
         <v>0</v>
@@ -12253,11 +12265,11 @@
       <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>AGG.NV01 | AGG.NV02 | AGG.NV03</t>
+          <t>AGI.NV01 | AGI.NV02 | AGI.NV03</t>
         </is>
       </c>
       <c r="K23" s="9" t="n">
-        <v>766</v>
+        <v>1889</v>
       </c>
       <c r="L23" s="20" t="n">
         <v>0</v>
@@ -12293,11 +12305,11 @@
       <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 00:00:10 | 2026-08-01 00:00:28 | 2026-08-01 00:00:36</t>
+          <t>2026-08-01 00:00:04 | 2026-08-01 00:00:08 | 2026-08-01 00:00:09</t>
         </is>
       </c>
       <c r="K24" s="9" t="n">
-        <v>2581920</v>
+        <v>2538911</v>
       </c>
       <c r="L24" s="20" t="n">
         <v>0</v>
@@ -12492,14 +12504,14 @@
     </row>
     <row r="38">
       <c r="B38" s="5" t="n">
-        <v>30000001</v>
+        <v>60000001</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>30050726</v>
+        <v>60002844</v>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>2026-CTO-T24-3000667/00</t>
+          <t>2026-DGT-XSC-6001806/00</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -12523,23 +12535,23 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>CTO.NV04</t>
+          <t>API.GREEN_SM</t>
         </is>
       </c>
       <c r="K38" s="26" t="n">
-        <v>46235.00011574074</v>
+        <v>46235.0000462963</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="5" t="n">
-        <v>30000002</v>
+        <v>60000002</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>30040170</v>
+        <v>60028548</v>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>2026-DGT-TXM-3003343/00</t>
+          <t>2026-DGT-XSC-6018131/00</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -12563,23 +12575,23 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>WEB.APP</t>
+          <t>API.GREEN_SM</t>
         </is>
       </c>
       <c r="K39" s="26" t="n">
-        <v>46235.00032407408</v>
+        <v>46235.00009259259</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="5" t="n">
-        <v>30000003</v>
+        <v>60000003</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>30013365</v>
+        <v>60052317</v>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>2026-DGT-TXM-3001132/00</t>
+          <t>2026-DGT-XSC-6033233/00</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -12603,23 +12615,23 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>API.VI_A</t>
+          <t>API.GREEN_SM</t>
         </is>
       </c>
       <c r="K40" s="26" t="n">
-        <v>46235.00041666667</v>
+        <v>46235.00010416667</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="5" t="n">
-        <v>30000004</v>
+        <v>60000004</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>30039442</v>
+        <v>60060394</v>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>2026-DGT-TXO-3000023/00</t>
+          <t>2026-DGT-XSC-6038333/00</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -12643,23 +12655,23 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>API.VI_A</t>
+          <t>API.GREEN_SM</t>
         </is>
       </c>
       <c r="K41" s="26" t="n">
-        <v>46235.00043981482</v>
+        <v>46235.00023148148</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="5" t="n">
-        <v>30000005</v>
+        <v>60000005</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>30051186</v>
+        <v>60031997</v>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>2026-DGT-T24-3010275/00</t>
+          <t>2026-DGT-XSC-6020284/00</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -12683,11 +12695,11 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>API.VT_A</t>
+          <t>API.GREEN_SM</t>
         </is>
       </c>
       <c r="K42" s="26" t="n">
-        <v>46235.00053240741</v>
+        <v>46235.00032407408</v>
       </c>
     </row>
   </sheetData>
@@ -12844,7 +12856,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>4844773</v>
+        <v>4127680</v>
       </c>
     </row>
     <row r="12">
@@ -12956,11 +12968,11 @@
       <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>30000001 | 30000002 | 30000003</t>
+          <t>60000001 | 60000002 | 60000003</t>
         </is>
       </c>
       <c r="K15" s="9" t="n">
-        <v>4844773</v>
+        <v>4127680</v>
       </c>
       <c r="L15" s="20" t="n">
         <v>0</v>
@@ -13000,11 +13012,11 @@
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>30000001 | 30000002 | 30000003</t>
+          <t>60000001 | 60000002 | 60000003</t>
         </is>
       </c>
       <c r="K16" s="9" t="n">
-        <v>4717930</v>
+        <v>4098401</v>
       </c>
       <c r="L16" s="20" t="n">
         <v>0</v>
@@ -13044,11 +13056,11 @@
       <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>CHN_BB | CHN_TN | NG_DL_ND</t>
+          <t>CHN_BB | CHN_TN | MV_DELAYCARE</t>
         </is>
       </c>
       <c r="K17" s="9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L17" s="20" t="n">
         <v>0</v>
@@ -13088,7 +13100,7 @@
         </is>
       </c>
       <c r="K18" s="9" t="n">
-        <v>41870</v>
+        <v>18381</v>
       </c>
       <c r="L18" s="20" t="n">
         <v>0</v>
@@ -13124,14 +13136,14 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>0.049993 | 0.049995 | 0.049997</t>
+          <t>0.049978 | 0.050000 | 0.050001</t>
         </is>
       </c>
       <c r="K19" s="9" t="n">
-        <v>124156</v>
+        <v>67009</v>
       </c>
       <c r="L19" s="20" t="n">
-        <v>0.4171813622640318</v>
+        <v>0.8220741433444453</v>
       </c>
     </row>
     <row r="20">
@@ -13168,7 +13180,7 @@
         </is>
       </c>
       <c r="K20" s="9" t="n">
-        <v>946</v>
+        <v>654</v>
       </c>
       <c r="L20" s="20" t="n">
         <v>0</v>
@@ -13208,11 +13220,11 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>0.00 | 100.00 | 10000.00</t>
+          <t>0.00 | 100.00 | 1000.00</t>
         </is>
       </c>
       <c r="K21" s="9" t="n">
-        <v>77374</v>
+        <v>95396</v>
       </c>
       <c r="L21" s="20" t="n">
         <v>0</v>
@@ -13248,11 +13260,11 @@
       <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>0 | 10000 | 100000</t>
+          <t>0 | 1000 | 10000</t>
         </is>
       </c>
       <c r="K22" s="9" t="n">
-        <v>77620</v>
+        <v>95524</v>
       </c>
       <c r="L22" s="20" t="n">
         <v>0</v>
@@ -13292,11 +13304,11 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>0 | -1000 | 100000</t>
+          <t>0 | 1000 | 10000</t>
         </is>
       </c>
       <c r="K23" s="9" t="n">
-        <v>56288</v>
+        <v>52027</v>
       </c>
       <c r="L23" s="20" t="n">
         <v>0</v>
@@ -13336,11 +13348,11 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>0.0000 | 0.0004 | 0.0013</t>
+          <t>0.0000 | 0.0067 | 0.0226</t>
         </is>
       </c>
       <c r="K24" s="9" t="n">
-        <v>180565</v>
+        <v>176803</v>
       </c>
       <c r="L24" s="20" t="n">
         <v>0</v>
@@ -13520,166 +13532,162 @@
     </row>
     <row r="38">
       <c r="B38" s="5" t="n">
-        <v>30000001</v>
+        <v>60000001</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>30000001</v>
+        <v>60000001</v>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>NG_TN24</t>
+          <t>MV_XSM_CARE</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>0.276667</v>
-      </c>
+        <v>500000000</v>
+      </c>
+      <c r="F38" s="5" t="inlineStr"/>
       <c r="G38" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>83000</v>
+        <v>1000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>83000</v>
+        <v>1000</v>
       </c>
       <c r="J38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>12.4749</v>
+        <v>9.5702</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="5" t="n">
-        <v>30000002</v>
+        <v>60000002</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>30000002</v>
+        <v>60000002</v>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>XE_TNDS_MOTO</t>
+          <t>MV_XSM_CARE</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>150000000</v>
+        <v>500000000</v>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
       <c r="G39" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>60000</v>
+        <v>1000</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>60000</v>
+        <v>1000</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>0</v>
+        <v>10.8353</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="5" t="n">
-        <v>30000003</v>
+        <v>60000003</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>30000003</v>
+        <v>60000003</v>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>XE_TNDS_MOTO</t>
+          <t>MV_XSM_CARE</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>150000000</v>
+        <v>500000000</v>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
       <c r="G40" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>60000</v>
+        <v>1000</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>60000</v>
+        <v>1000</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>11.1279</v>
+        <v>11.2706</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="5" t="n">
-        <v>30000004</v>
+        <v>60000004</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>30000004</v>
+        <v>60000004</v>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>XE_TNDS_OTO</t>
+          <t>MV_XSM_CARE</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>150000000</v>
+        <v>500000000</v>
       </c>
       <c r="F41" s="5" t="inlineStr"/>
       <c r="G41" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>756000</v>
+        <v>2000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>756000</v>
+        <v>2000</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>75600</v>
+        <v>0</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>2.3195</v>
+        <v>8.7582</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="5" t="n">
-        <v>30000005</v>
+        <v>60000005</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>30000005</v>
+        <v>60000005</v>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>NG_TN24</t>
+          <t>MV_XSM_CARE</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>0.25</v>
-      </c>
+        <v>500000000</v>
+      </c>
+      <c r="F42" s="5" t="inlineStr"/>
       <c r="G42" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>75000</v>
+        <v>2000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>75000</v>
+        <v>2000</v>
       </c>
       <c r="J42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>7.6517</v>
+        <v>13.3531</v>
       </c>
     </row>
   </sheetData>
@@ -13835,7 +13843,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>4670512</v>
+        <v>4082967</v>
       </c>
     </row>
     <row r="12">
@@ -13951,11 +13959,11 @@
       <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>30000001 | 30000002 | 30000003</t>
+          <t>60000001 | 60000002 | 60000003</t>
         </is>
       </c>
       <c r="K15" s="9" t="n">
-        <v>4669144</v>
+        <v>4082637</v>
       </c>
       <c r="L15" s="20" t="n">
         <v>0</v>
@@ -14087,11 +14095,11 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>0.4100 | 0.6100 | 0.8800</t>
+          <t>10.0000 | 100.0000 | 10.0900</t>
         </is>
       </c>
       <c r="K18" s="9" t="n">
-        <v>1011</v>
+        <v>290</v>
       </c>
       <c r="L18" s="20" t="n">
         <v>0</v>
@@ -14241,7 +14249,7 @@
     </row>
     <row r="32">
       <c r="B32" s="5" t="n">
-        <v>30000001</v>
+        <v>60000001</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
@@ -14259,7 +14267,7 @@
     </row>
     <row r="33">
       <c r="B33" s="5" t="n">
-        <v>30000002</v>
+        <v>60000002</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
@@ -14277,7 +14285,7 @@
     </row>
     <row r="34">
       <c r="B34" s="5" t="n">
-        <v>30000003</v>
+        <v>60000003</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
@@ -14295,7 +14303,7 @@
     </row>
     <row r="35">
       <c r="B35" s="5" t="n">
-        <v>30000004</v>
+        <v>60000004</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
@@ -14313,7 +14321,7 @@
     </row>
     <row r="36">
       <c r="B36" s="5" t="n">
-        <v>30000005</v>
+        <v>60000005</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
@@ -14482,7 +14490,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>4991277</v>
+        <v>4152252</v>
       </c>
     </row>
     <row r="12">
@@ -14598,11 +14606,11 @@
       <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>30000001 | 30000002 | 30000003</t>
+          <t>60000001 | 60000002 | 60000003</t>
         </is>
       </c>
       <c r="K15" s="9" t="n">
-        <v>4669144</v>
+        <v>4082637</v>
       </c>
       <c r="L15" s="20" t="n">
         <v>0</v>
@@ -14646,11 +14654,11 @@
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>AGG | BNH | CTO</t>
+          <t>AGI | ALC | BTB</t>
         </is>
       </c>
       <c r="K16" s="9" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="L16" s="20" t="n">
         <v>0</v>
@@ -14906,11 +14914,11 @@
     </row>
     <row r="33">
       <c r="B33" s="5" t="n">
-        <v>30000001</v>
+        <v>60000001</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>HN2</t>
+          <t>DGT</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -14924,11 +14932,11 @@
     </row>
     <row r="34">
       <c r="B34" s="5" t="n">
-        <v>30000002</v>
+        <v>60000002</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DGT</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -14942,11 +14950,11 @@
     </row>
     <row r="35">
       <c r="B35" s="5" t="n">
-        <v>30000003</v>
+        <v>60000003</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>DGT</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -14960,11 +14968,11 @@
     </row>
     <row r="36">
       <c r="B36" s="5" t="n">
-        <v>30000004</v>
+        <v>60000004</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>HN3</t>
+          <t>DGT</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -14978,11 +14986,11 @@
     </row>
     <row r="37">
       <c r="B37" s="5" t="n">
-        <v>30000005</v>
+        <v>60000005</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DGT</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -15026,7 +15034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15039,7 +15047,7 @@
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="47" customWidth="1" min="11" max="11"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
     <col width="48" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -15053,7 +15061,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sinh tự động từ catalog PostgreSQL reportapi — bronze.ins_* (v2/docs/build_docs.py, DOCS_TARGET=volume) ngày 16/10/2026. Tên bảng ghi theo mô hình logic: ref.X / core.X = bronze.ins_X.</t>
+          <t>Sinh tự động từ catalog PostgreSQL reportapi — bronze.ins_* (scripts/build_docs.py, DOCS_TARGET=volume) ngày 19/10/2026. Tên bảng ghi theo mô hình logic: ref.X / core.X = bronze.ins_X.</t>
         </is>
       </c>
     </row>
@@ -15463,12 +15471,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>NG_DL_ND</t>
+          <t>MV_DELAYCARE</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm du lịch trong nước</t>
+          <t>Bảo hiểm trễ chuyến bay (DelayCare)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -15509,7 +15517,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>1 Medical expense insurance (*)</t>
+          <t>12 Miscellaneous financial loss (*)</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
@@ -15521,12 +15529,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>NG_DL_QT</t>
+          <t>NG_DL_ND</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm du lịch quốc tế</t>
+          <t>Bảo hiểm du lịch trong nước</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -15579,17 +15587,17 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>NG_NVV</t>
+          <t>NG_DL_QT</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm người vay vốn</t>
+          <t>Bảo hiểm du lịch quốc tế</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>BH sinh mạng – tai nạn</t>
+          <t>BH du lịch</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -15604,7 +15612,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>A.1</t>
+          <t>A.2</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -15614,7 +15622,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>RATE_ON_SI</t>
+          <t>PER_PERSON</t>
         </is>
       </c>
       <c r="I13" s="5" t="n">
@@ -15625,7 +15633,7 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>2 Income protection insurance (*)</t>
+          <t>1 Medical expense insurance (*)</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
@@ -15637,12 +15645,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>NG_SM_CN</t>
+          <t>MV_FOOD_CARE</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm sinh mạng cá nhân</t>
+          <t>Bảo hiểm đơn giao đồ ăn (Food Care)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -15672,7 +15680,7 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>RATE_ON_SI</t>
+          <t>PER_PERSON</t>
         </is>
       </c>
       <c r="I14" s="5" t="n">
@@ -15695,12 +15703,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>NG_TN24</t>
+          <t>MV_XSM_CARE</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm tai nạn con người 24/24</t>
+          <t>Bảo hiểm tai nạn hành khách theo chuyến xe công nghệ (Green SM Care)</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -15730,7 +15738,7 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>RATE_ON_SI</t>
+          <t>PER_PERSON</t>
         </is>
       </c>
       <c r="I15" s="5" t="n">
@@ -15753,17 +15761,17 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>NG_SK_BHN</t>
+          <t>NG_NVV</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm bệnh hiểm nghèo – ung thư</t>
+          <t>Bảo hiểm người vay vốn</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>BH sức khỏe</t>
+          <t>BH sinh mạng – tai nạn</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -15788,7 +15796,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>PER_PERSON</t>
+          <t>RATE_ON_SI</t>
         </is>
       </c>
       <c r="I16" s="5" t="n">
@@ -15811,17 +15819,17 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>NG_SK_CN</t>
+          <t>NG_SM_CN</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm sức khỏe cá nhân</t>
+          <t>Bảo hiểm sinh mạng cá nhân</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>BH sức khỏe</t>
+          <t>BH sinh mạng – tai nạn</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -15836,7 +15844,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>A.2</t>
+          <t>A.1</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -15846,7 +15854,7 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>PER_PERSON</t>
+          <t>RATE_ON_SI</t>
         </is>
       </c>
       <c r="I17" s="5" t="n">
@@ -15857,7 +15865,7 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>1 Medical expense insurance</t>
+          <t>2 Income protection insurance (*)</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
@@ -15869,17 +15877,17 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>NG_SK_NHOM</t>
+          <t>NG_TN24</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm sức khỏe nhóm doanh nghiệp</t>
+          <t>Bảo hiểm tai nạn con người 24/24</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>BH sức khỏe</t>
+          <t>BH sinh mạng – tai nạn</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -15894,7 +15902,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>A.2</t>
+          <t>A.1</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -15904,7 +15912,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>PER_PERSON</t>
+          <t>RATE_ON_SI</t>
         </is>
       </c>
       <c r="I18" s="5" t="n">
@@ -15915,7 +15923,7 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>1 Medical expense insurance</t>
+          <t>2 Income protection insurance (*)</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -15927,32 +15935,32 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>TS_MRR</t>
+          <t>NG_SK_BHN</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm mọi rủi ro tài sản</t>
+          <t>Bảo hiểm bệnh hiểm nghèo – ung thư</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>BH tài sản</t>
+          <t>BH sức khỏe</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm tài sản</t>
+          <t>Bảo hiểm sức khỏe</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Tài sản</t>
+          <t>Con người</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>B.1b</t>
+          <t>A.1</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -15962,51 +15970,55 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>RATE_ON_SI</t>
+          <t>PER_PERSON</t>
         </is>
       </c>
       <c r="I19" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>7 Fire and other damage to property insurance</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr"/>
+          <t>2 Income protection insurance (*)</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Không chịu thuế GTGT – Luật Thuế GTGT 48/2024/QH15 Điều 5 k8</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>TS_MRRCN</t>
+          <t>NG_SK_CN</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm mọi rủi ro công nghiệp</t>
+          <t>Bảo hiểm sức khỏe cá nhân</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>BH tài sản</t>
+          <t>BH sức khỏe</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm tài sản</t>
+          <t>Bảo hiểm sức khỏe</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Tài sản</t>
+          <t>Con người</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>B.1b</t>
+          <t>A.2</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -16016,51 +16028,55 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>RATE_ON_SI</t>
+          <t>PER_PERSON</t>
         </is>
       </c>
       <c r="I20" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>7 Fire and other damage to property insurance</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr"/>
+          <t>1 Medical expense insurance</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Không chịu thuế GTGT – Luật Thuế GTGT 48/2024/QH15 Điều 5 k8</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>TS_NHA</t>
+          <t>NG_SK_NHOM</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm nhà tư nhân</t>
+          <t>Bảo hiểm sức khỏe nhóm doanh nghiệp</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>BH tài sản</t>
+          <t>BH sức khỏe</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm tài sản</t>
+          <t>Bảo hiểm sức khỏe</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Tài sản</t>
+          <t>Con người</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>B.1b</t>
+          <t>A.2</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -16070,41 +16086,45 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>RATE_ON_SI</t>
+          <t>PER_PERSON</t>
         </is>
       </c>
       <c r="I21" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>7 Fire and other damage to property insurance</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr"/>
+          <t>1 Medical expense insurance</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>Không chịu thuế GTGT – Luật Thuế GTGT 48/2024/QH15 Điều 5 k8</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>CHN_BB</t>
+          <t>MV_TBDT_TMDT</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm cháy, nổ bắt buộc</t>
+          <t>Bảo hiểm thiết bị điện tử mua trên sàn TMĐT</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>BH cháy nổ</t>
+          <t>BH tài sản</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm cháy, nổ</t>
+          <t>Bảo hiểm tài sản</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -16114,12 +16134,12 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>B.5a</t>
+          <t>B.1b</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -16135,34 +16155,30 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>7 Fire and other damage to property insurance</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>NĐ 67/2023/NĐ-CP Phụ lục II; thay thế bởi NĐ 105/2025/NĐ-CP Phụ lục VI từ 01/7/2</t>
-        </is>
-      </c>
+          <t>7 Fire and other damage to property insurance (*)</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>CHN_TN</t>
+          <t>TS_MRR</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm cháy và các rủi ro đặc biệt (tự nguyện)</t>
+          <t>Bảo hiểm mọi rủi ro tài sản</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>BH cháy nổ</t>
+          <t>BH tài sản</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Bảo hiểm cháy, nổ</t>
+          <t>Bảo hiểm tài sản</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -16172,7 +16188,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>B.5b</t>
+          <t>B.1b</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -16189,14 +16205,234 @@
         <v>10</v>
       </c>
       <c r="J23" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>7 Fire and other damage to property insurance</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>TS_MRRCN</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm mọi rủi ro công nghiệp</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>BH tài sản</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm tài sản</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Tài sản</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>B.1b</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>RATE_ON_SI</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="J24" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>7 Fire and other damage to property insurance</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TS_NHA</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm nhà tư nhân</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>BH tài sản</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm tài sản</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Tài sản</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>B.1b</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>RATE_ON_SI</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>7 Fire and other damage to property insurance</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>CHN_BB</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm cháy, nổ bắt buộc</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>BH cháy nổ</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm cháy, nổ</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Tài sản</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>B.5a</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>RATE_ON_SI</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>7 Fire and other damage to property insurance</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>NĐ 67/2023/NĐ-CP Phụ lục II; thay thế bởi NĐ 105/2025/NĐ-CP Phụ lục VI từ 01/7/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>CHN_TN</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm cháy và các rủi ro đặc biệt (tự nguyện)</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>BH cháy nổ</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm cháy, nổ</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Tài sản</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>B.5b</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>RATE_ON_SI</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>7 Fire and other damage to property insurance</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16209,15 +16445,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -16231,7 +16467,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sinh tự động từ catalog PostgreSQL reportapi — bronze.ins_* (v2/docs/build_docs.py, DOCS_TARGET=volume) ngày 16/10/2026. Tên bảng ghi theo mô hình logic: ref.X / core.X = bronze.ins_X.</t>
+          <t>Sinh tự động từ catalog PostgreSQL reportapi — bronze.ins_* (scripts/build_docs.py, DOCS_TARGET=volume) ngày 19/10/2026. Tên bảng ghi theo mô hình logic: ref.X / core.X = bronze.ins_X.</t>
         </is>
       </c>
     </row>
@@ -17513,17 +17749,17 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>HK_A</t>
+          <t>ATADI</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Hãng hàng không A</t>
+          <t>ATADI.vn – đại lý vé máy bay trực tuyến</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>HANG_HANG_KHONG</t>
+          <t>OTA_VE_MAY_BAY</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -17550,17 +17786,17 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>TMDT_A</t>
+          <t>FUSE</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Sàn thương mại điện tử A</t>
+          <t>Fuse – nền tảng phân phối bảo hiểm trên Shopee, Lazada</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>SAN_TMDT</t>
+          <t>INSURTECH</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -17587,17 +17823,17 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>VI_A</t>
+          <t>GREEN_SM</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Ví điện tử A</t>
+          <t>Green SM (Xanh SM) – nền tảng gọi xe, giao đồ ăn</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>VI_DIEN_TU</t>
+          <t>NEN_TANG_DI_CHUYEN</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -17624,17 +17860,17 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>VI_B</t>
+          <t>HK_A</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Ví điện tử B</t>
+          <t>Hãng hàng không A</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>VI_DIEN_TU</t>
+          <t>HANG_HANG_KHONG</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -17661,20 +17897,131 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
+          <t>TMDT_A</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Sàn thương mại điện tử A</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>SAN_TMDT</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Luật KDBH 2022 (08/2022/QH15) Điều 87 k4 điểm d; TT 67/2023/TT-BTC Điều 4–5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>DIEN_TU</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Giao dịch điện tử (website/app, nền tảng đối tác)</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Qua môi trường mạng</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>VI_A</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Ví điện tử A</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>VI_DIEN_TU</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Luật KDBH 2022 (08/2022/QH15) Điều 87 k4 điểm d; TT 67/2023/TT-BTC Điều 4–5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>DIEN_TU</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Giao dịch điện tử (website/app, nền tảng đối tác)</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Qua môi trường mạng</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>VI_B</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Ví điện tử B</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>VI_DIEN_TU</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Luật KDBH 2022 (08/2022/QH15) Điều 87 k4 điểm d; TT 67/2023/TT-BTC Điều 4–5</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>DIEN_TU</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Giao dịch điện tử (website/app, nền tảng đối tác)</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Qua môi trường mạng</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
           <t>VT_A</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>Nhà mạng viễn thông A</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>VIEN_THONG</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>Luật KDBH 2022 (08/2022/QH15) Điều 87 k4 điểm d; TT 67/2023/TT-BTC Điều 4–5</t>
         </is>
@@ -17713,7 +18060,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sinh tự động từ catalog PostgreSQL reportapi — bronze.ins_* (v2/docs/build_docs.py, DOCS_TARGET=volume) ngày 16/10/2026. Tên bảng ghi theo mô hình logic: ref.X / core.X = bronze.ins_X.</t>
+          <t>Sinh tự động từ catalog PostgreSQL reportapi — bronze.ins_* (scripts/build_docs.py, DOCS_TARGET=volume) ngày 19/10/2026. Tên bảng ghi theo mô hình logic: ref.X / core.X = bronze.ins_X.</t>
         </is>
       </c>
     </row>
@@ -18028,7 +18375,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sinh tự động từ catalog PostgreSQL reportapi — bronze.ins_* (v2/docs/build_docs.py, DOCS_TARGET=volume) ngày 16/10/2026. Tên bảng ghi theo mô hình logic: ref.X / core.X = bronze.ins_X.</t>
+          <t>Sinh tự động từ catalog PostgreSQL reportapi — bronze.ins_* (scripts/build_docs.py, DOCS_TARGET=volume) ngày 19/10/2026. Tên bảng ghi theo mô hình logic: ref.X / core.X = bronze.ins_X.</t>
         </is>
       </c>
     </row>
@@ -18943,7 +19290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18964,7 +19311,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sinh tự động từ catalog PostgreSQL reportapi — bronze.ins_* (v2/docs/build_docs.py, DOCS_TARGET=volume) ngày 16/10/2026. Tên bảng ghi theo mô hình logic: ref.X / core.X = bronze.ins_X.</t>
+          <t>Sinh tự động từ catalog PostgreSQL reportapi — bronze.ins_* (scripts/build_docs.py, DOCS_TARGET=volume) ngày 19/10/2026. Tên bảng ghi theo mô hình logic: ref.X / core.X = bronze.ins_X.</t>
         </is>
       </c>
     </row>
@@ -19004,12 +19351,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Tổng công ty Bảo hiểm DEMO (doanh nghiệp giả lập)</t>
+          <t>Tổng Công ty Bảo hiểm PVI</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -19037,7 +19384,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Trung tâm Kinh doanh số</t>
+          <t>Bảo hiểm PVI Digital</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -19047,11 +19394,19 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Miền Nam</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -19061,7 +19416,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Khối Trụ sở chính – Ban Kinh doanh trực tiếp</t>
+          <t>Trụ sở chính Tổng Công ty Bảo hiểm PVI – các Ban kinh doanh</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -19071,7 +19426,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -19088,12 +19443,12 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO An Giang</t>
+          <t>Bảo hiểm PVI An Giang</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -19103,7 +19458,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -19120,12 +19475,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>ALC</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO Bắc Ninh</t>
+          <t>Bảo hiểm PVI Âu Lạc</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -19135,12 +19490,12 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Tỉnh Bắc Ninh</t>
+          <t>Thành phố Hà Nội</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -19152,12 +19507,12 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>BTB</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO Cần Thơ</t>
+          <t>Bảo hiểm PVI Bắc Trung Bộ</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -19167,29 +19522,29 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Thành phố Cần Thơ</t>
+          <t>Tỉnh Nghệ An</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Miền Nam</t>
+          <t>Miền Trung</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>BTH</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO Đắk Lắk</t>
+          <t>Bảo hiểm PVI Bến Thành</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -19199,29 +19554,29 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Tỉnh Đắk Lắk</t>
+          <t>Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Miền Trung</t>
+          <t>Miền Nam</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CLG</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO Đà Nẵng</t>
+          <t>Bảo hiểm PVI Cửu Long</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -19231,29 +19586,29 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Thành phố Đà Nẵng</t>
+          <t>Tỉnh Vĩnh Long</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Miền Trung</t>
+          <t>Miền Nam</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO Đồng Nai</t>
+          <t>Bảo hiểm PVI Cà Mau</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -19263,12 +19618,12 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Tỉnh Đồng Nai</t>
+          <t>Tỉnh Cà Mau</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -19280,12 +19635,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>HC1</t>
+          <t>DDO</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO TP. Hồ Chí Minh</t>
+          <t>Bảo hiểm PVI Đông Đô</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -19295,29 +19650,29 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Thành phố Hồ Chí Minh</t>
+          <t>Thành phố Hà Nội</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Miền Nam</t>
+          <t>Miền Bắc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>HC2</t>
+          <t>DHI</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO Đông TP. Hồ Chí Minh</t>
+          <t>Bảo hiểm PVI Duyên Hải</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -19327,29 +19682,29 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Thành phố Hồ Chí Minh</t>
+          <t>Thành phố Hải Phòng</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Miền Nam</t>
+          <t>Miền Bắc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>HC3</t>
+          <t>DKH</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO Bình Dương</t>
+          <t>Bảo hiểm PVI Đồng Khởi</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -19359,7 +19714,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -19376,12 +19731,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>HN1</t>
+          <t>DNA</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO Hà Nội</t>
+          <t>Bảo hiểm PVI Đà Nẵng</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -19391,29 +19746,29 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Thành phố Hà Nội</t>
+          <t>Thành phố Đà Nẵng</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Miền Bắc</t>
+          <t>Miền Trung</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>HN2</t>
+          <t>DNB</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO Bắc Hà Nội</t>
+          <t>Bảo hiểm PVI Đông Nam Bộ</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -19423,29 +19778,29 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Thành phố Hà Nội</t>
+          <t>Tỉnh Đồng Nai</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Miền Bắc</t>
+          <t>Miền Nam</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>HN3</t>
+          <t>DSG</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO Tây Hà Nội</t>
+          <t>Bảo hiểm PVI Đông Sài Gòn</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -19455,29 +19810,29 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Thành phố Hà Nội</t>
+          <t>Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Miền Bắc</t>
+          <t>Miền Nam</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DTH</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO Hải Phòng</t>
+          <t>Bảo hiểm PVI Đồng Tháp</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -19487,29 +19842,29 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Thành phố Hải Phòng</t>
+          <t>Tỉnh Đồng Tháp</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Miền Bắc</t>
+          <t>Miền Nam</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>HUE</t>
+          <t>GDI</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO Huế</t>
+          <t>Bảo hiểm PVI Gia Định</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -19519,29 +19874,29 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Thành phố Huế</t>
+          <t>Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Miền Trung</t>
+          <t>Miền Nam</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>GLA</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO Khánh Hòa</t>
+          <t>Bảo hiểm PVI Gia Lai</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -19551,12 +19906,12 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Tỉnh Khánh Hòa</t>
+          <t>Tỉnh Gia Lai</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -19568,12 +19923,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HHG</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO Nghệ An</t>
+          <t>Bảo hiểm PVI Hải Hưng</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -19583,29 +19938,29 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Tỉnh Nghệ An</t>
+          <t>Tỉnh Hưng Yên</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Miền Trung</t>
+          <t>Miền Bắc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>HNO</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO Quảng Ninh</t>
+          <t>Bảo hiểm PVI Hà Nội</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -19615,12 +19970,12 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Tỉnh Quảng Ninh</t>
+          <t>Thành phố Hà Nội</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -19632,12 +19987,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>HTA</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO Thanh Hóa</t>
+          <t>Bảo hiểm PVI Hà Thành</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -19647,17 +20002,913 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>Thành phố Hà Nội</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Miền Bắc</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>HTI</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Hà Tĩnh</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Tỉnh Hà Tĩnh</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Miền Trung</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>KBC</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Kinh Bắc</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Tỉnh Bắc Ninh</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Miền Bắc</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>KHO</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Khánh Hoà</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Tỉnh Khánh Hòa</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Miền Trung</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>LDO</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Lâm Đồng</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Tỉnh Lâm Đồng</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Miền Trung</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>LNK</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Link</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Thành phố Hà Nội</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Miền Bắc</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>NBI</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Ninh Bình</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Tỉnh Ninh Bình</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Miền Bắc</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>NDN</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Nam Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Thành phố Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Miền Trung</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>NSG</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Nam Sài Gòn</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Miền Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>NTB</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Nam Trung Bộ</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Tỉnh Quảng Ngãi</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Miền Trung</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>PNA</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Phía Nam</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Miền Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>QNI</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Quảng Ninh</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Tỉnh Quảng Ninh</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Miền Bắc</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>QTI</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Quảng Trị</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Tỉnh Quảng Trị</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Miền Trung</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>SGN</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Sài Gòn</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Miền Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TAN</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Tràng An</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Thành phố Hà Nội</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Miền Bắc</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>TDH</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Thành Đô</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Miền Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TDO</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Thủ Đô</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Thành phố Hà Nội</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Miền Bắc</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>TDU</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Thủ Đức</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Miền Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>THO</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Thanh Hóa</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
           <t>Tỉnh Thanh Hóa</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>Miền Trung</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>TLG</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Thăng Long</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Thành phố Hà Nội</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Miền Bắc</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TNA</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Tây Nam</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Thành phố Cần Thơ</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Miền Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>TNG</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Tây Nguyên</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Tỉnh Đắk Lắk</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Miền Trung</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TNT</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Thống Nhất</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Miền Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>TNU</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Thái Nguyên</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Tỉnh Thái Nguyên</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Miền Bắc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>TPH</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI TP. Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Miền Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>TTH</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Huế</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Thành phố Huế</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Miền Trung</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>TYN</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Tây Ninh</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Tỉnh Tây Ninh</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Miền Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>VPU</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Vĩnh Phú</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Tỉnh Phú Thọ</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Miền Bắc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>VTU</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Miền Nam</t>
         </is>
       </c>
     </row>
@@ -19691,7 +20942,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sinh tự động từ catalog PostgreSQL reportapi — bronze.ins_* (v2/docs/build_docs.py, DOCS_TARGET=volume) ngày 16/10/2026. Tên bảng ghi theo mô hình logic: ref.X / core.X = bronze.ins_X.</t>
+          <t>Sinh tự động từ catalog PostgreSQL reportapi — bronze.ins_* (scripts/build_docs.py, DOCS_TARGET=volume) ngày 19/10/2026. Tên bảng ghi theo mô hình logic: ref.X / core.X = bronze.ins_X.</t>
         </is>
       </c>
     </row>
@@ -20048,7 +21299,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sinh tự động từ catalog PostgreSQL reportapi — bronze.ins_* (v2/docs/build_docs.py, DOCS_TARGET=volume) ngày 16/10/2026. Tên bảng ghi theo mô hình logic: ref.X / core.X = bronze.ins_X.</t>
+          <t>Sinh tự động từ catalog PostgreSQL reportapi — bronze.ins_* (scripts/build_docs.py, DOCS_TARGET=volume) ngày 19/10/2026. Tên bảng ghi theo mô hình logic: ref.X / core.X = bronze.ins_X.</t>
         </is>
       </c>
     </row>
@@ -20465,7 +21716,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sinh tự động từ catalog PostgreSQL reportapi — bronze.ins_* (v2/docs/build_docs.py, DOCS_TARGET=volume) ngày 16/10/2026. Tên bảng ghi theo mô hình logic: ref.X / core.X = bronze.ins_X.</t>
+          <t>Sinh tự động từ catalog PostgreSQL reportapi — bronze.ins_* (scripts/build_docs.py, DOCS_TARGET=volume) ngày 19/10/2026. Tên bảng ghi theo mô hình logic: ref.X / core.X = bronze.ins_X.</t>
         </is>
       </c>
     </row>
@@ -21948,7 +23199,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -22060,11 +23311,11 @@
       <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>AGG | BNH | CTO</t>
+          <t>AGI | ALC | BTB</t>
         </is>
       </c>
       <c r="K15" s="9" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="L15" s="20" t="n">
         <v>0</v>
@@ -22100,11 +23351,11 @@
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO An Giang | Công ty Bảo hiểm DEMO Bắc Hà Nội | Công ty Bảo hiểm DEMO Bắc Ninh</t>
+          <t>Bảo hiểm PVI An Giang | Bảo hiểm PVI Âu Lạc | Bảo hiểm PVI Bắc Trung Bộ</t>
         </is>
       </c>
       <c r="K16" s="9" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="L16" s="20" t="n">
         <v>0</v>
@@ -22180,14 +23431,14 @@
       <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="K18" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.02040816326530612</v>
       </c>
     </row>
     <row r="19">
@@ -22220,14 +23471,14 @@
       <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>AGG | BNH | CTO</t>
+          <t>AGG | BNH | CMU</t>
         </is>
       </c>
       <c r="K19" s="9" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="L19" s="20" t="n">
-        <v>0.04761904761904762</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -22256,11 +23507,11 @@
       <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>2005-01-01 | 2005-04-01 | 2006-02-01</t>
+          <t>2005-01-01 | 2005-04-01 | 2005-07-01</t>
         </is>
       </c>
       <c r="K20" s="9" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="L20" s="20" t="n">
         <v>0</v>
@@ -22502,42 +23753,42 @@
     <row r="37">
       <c r="B37" s="5" t="inlineStr">
         <is>
+          <t>AGI</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Bảo hiểm PVI An Giang</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
           <t>AGG</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Công ty Bảo hiểm DEMO An Giang</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>MEMBER</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>DEMO</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>AGG</t>
-        </is>
-      </c>
       <c r="G37" s="24" t="n">
-        <v>40026</v>
+        <v>43709</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>ALC</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO Bắc Ninh</t>
+          <t>Bảo hiểm PVI Âu Lạc</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -22547,27 +23798,27 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="G38" s="24" t="n">
-        <v>41122</v>
+        <v>41518</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>BTB</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Công ty Bảo hiểm DEMO Cần Thơ</t>
+          <t>Bảo hiểm PVI Bắc Trung Bộ</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -22577,68 +23828,76 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>PVI</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="G39" s="24" t="n">
-        <v>39630</v>
+        <v>41214</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
+          <t>BTH</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Tổng công ty Bảo hiểm DEMO (doanh nghiệp giả lập)</t>
+          <t>Bảo hiểm PVI Bến Thành</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>CORPORATION</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr"/>
+          <t>MEMBER</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>PVI</t>
+        </is>
+      </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="G40" s="24" t="n">
-        <v>38353</v>
+        <v>43221</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>DGT</t>
+          <t>CLG</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Trung tâm Kinh doanh số</t>
+          <t>Bảo hiểm PVI Cửu Long</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>DIGITAL</t>
+          <t>MEMBER</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>DEMO</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr"/>
+          <t>PVI</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>VLG</t>
+        </is>
+      </c>
       <c r="G41" s="24" t="n">
-        <v>38749</v>
+        <v>41334</v>
       </c>
     </row>
   </sheetData>
